--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1067,7 +1067,7 @@
           <t>audio_type</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>volume_scale</t>
         </is>
@@ -1094,7 +1094,7 @@
           <t>int</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1121,7 +1121,7 @@
           <t>类型0音效 1音乐 2环境音</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>音效音量缩放(0或空=1)</t>
         </is>
@@ -1396,6 +1396,9 @@
       <c r="D18" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="E18" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
@@ -2512,7 +2515,7 @@
       <c r="D80" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1144,6 +1144,9 @@
       <c r="D4" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
@@ -1396,7 +1399,7 @@
       <c r="D18" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1848,6 +1851,9 @@
       </c>
       <c r="D43" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="44">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1144,7 +1144,7 @@
       <c r="D4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       <c r="D43" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -2815,70 +2815,70 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>1000001</v>
+        <v>580001</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>music_fight_1.wav</t>
+          <t>sound_win_1.wav</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐1</t>
+          <t>胜利1</t>
         </is>
       </c>
       <c r="D97" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>1000002</v>
+        <v>580003</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>sound_win_3.wav</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>胜利3</t>
         </is>
       </c>
       <c r="D98" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="0" t="n">
-        <v>1000003</v>
-      </c>
-      <c r="B99" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_3.wav</t>
-        </is>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐3</t>
-        </is>
-      </c>
-      <c r="D99" s="0" t="n">
-        <v>1</v>
+      <c r="A99" t="n">
+        <v>580004</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>sound_win_4.wav</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>胜利4</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>1000004</v>
+        <v>1000001</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>music_fight_4.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐4</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D100" s="0" t="n">
@@ -2887,16 +2887,16 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>1000005</v>
+        <v>1000002</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D101" s="0" t="n">
@@ -2905,16 +2905,16 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>1000006</v>
+        <v>1000003</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D102" s="0" t="n">
@@ -2923,16 +2923,16 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="n">
-        <v>1000007</v>
+        <v>1000004</v>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D103" s="0" t="n">
@@ -2941,16 +2941,16 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>1000008</v>
+        <v>1000005</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D104" s="0" t="n">
@@ -2959,16 +2959,16 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>1000009</v>
+        <v>1000006</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D105" s="0" t="n">
@@ -2977,16 +2977,16 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>1000010</v>
+        <v>1000007</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D106" s="0" t="n">
@@ -2995,16 +2995,16 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>1000011</v>
+        <v>1000008</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D107" s="0" t="n">
@@ -3013,16 +3013,16 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>1100001</v>
+        <v>1000009</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D108" s="0" t="n">
@@ -3031,16 +3031,16 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>1100002</v>
+        <v>1000010</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D109" s="0" t="n">
@@ -3049,16 +3049,16 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>1100003</v>
+        <v>1000011</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D110" s="0" t="n">
@@ -3067,16 +3067,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>1100004</v>
+        <v>1100001</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D111" s="0" t="n">
@@ -3085,16 +3085,16 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>1100005</v>
+        <v>1100002</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D112" s="0" t="n">
@@ -3103,16 +3103,16 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>1100006</v>
+        <v>1100003</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D113" s="0" t="n">
@@ -3121,16 +3121,16 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>1100007</v>
+        <v>1100004</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D114" s="0" t="n">
@@ -3139,16 +3139,16 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>1100008</v>
+        <v>1100005</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D115" s="0" t="n">
@@ -3157,16 +3157,16 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>1100009</v>
+        <v>1100006</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D116" s="0" t="n">
@@ -3175,16 +3175,16 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D117" s="0" t="n">
@@ -3193,16 +3193,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>1100011</v>
+        <v>1100008</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D118" s="0" t="n">
@@ -3211,16 +3211,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>1100012</v>
+        <v>1100009</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D119" s="0" t="n">
@@ -3229,16 +3229,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>1100013</v>
+        <v>1100010</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_10.wav</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐10</t>
         </is>
       </c>
       <c r="D120" s="0" t="n">
@@ -3247,19 +3247,73 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="B121" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_11.mp3</t>
+        </is>
+      </c>
+      <c r="C121" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐11</t>
+        </is>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="B122" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_12.mp3</t>
+        </is>
+      </c>
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐12</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B123" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B121" s="0" t="inlineStr">
+      <c r="B124" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C121" s="0" t="inlineStr">
+      <c r="C124" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D121" s="0" t="n">
+      <c r="D124" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -2686,6 +2686,9 @@
       <c r="D89" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="E89" s="0" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
@@ -2850,107 +2853,107 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="0" t="n">
         <v>580004</v>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>sound_win_4.wav</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="0" t="inlineStr">
         <is>
           <t>胜利4</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>1000001</v>
+        <v>590001</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>music_fight_1.wav</t>
+          <t>sound_continuous_1.wav</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐1</t>
+          <t>持续1</t>
         </is>
       </c>
       <c r="D100" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>1000002</v>
+        <v>600001</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>sound_magic_1.wav</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>魔法1</t>
         </is>
       </c>
       <c r="D101" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>1000003</v>
+        <v>600002</v>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>music_fight_3.wav</t>
+          <t>sound_magic_2.wav</t>
         </is>
       </c>
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐3</t>
+          <t>魔法2</t>
         </is>
       </c>
       <c r="D102" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="0" t="n">
-        <v>1000004</v>
-      </c>
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_4.wav</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐4</t>
-        </is>
-      </c>
-      <c r="D103" s="0" t="n">
-        <v>1</v>
+      <c r="A103" t="n">
+        <v>600003</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>sound_magic_3.wav</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>魔法3</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>1000005</v>
+        <v>1000001</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D104" s="0" t="n">
@@ -2959,16 +2962,16 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="n">
-        <v>1000006</v>
+        <v>1000002</v>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D105" s="0" t="n">
@@ -2977,16 +2980,16 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="n">
-        <v>1000007</v>
+        <v>1000003</v>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D106" s="0" t="n">
@@ -2995,16 +2998,16 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="n">
-        <v>1000008</v>
+        <v>1000004</v>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D107" s="0" t="n">
@@ -3013,16 +3016,16 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="n">
-        <v>1000009</v>
+        <v>1000005</v>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D108" s="0" t="n">
@@ -3031,16 +3034,16 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="n">
-        <v>1000010</v>
+        <v>1000006</v>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D109" s="0" t="n">
@@ -3049,16 +3052,16 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>1000011</v>
+        <v>1000007</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D110" s="0" t="n">
@@ -3067,16 +3070,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>1100001</v>
+        <v>1000008</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D111" s="0" t="n">
@@ -3085,16 +3088,16 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>1100002</v>
+        <v>1000009</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D112" s="0" t="n">
@@ -3103,16 +3106,16 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>1100003</v>
+        <v>1000010</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D113" s="0" t="n">
@@ -3121,16 +3124,16 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>1100004</v>
+        <v>1000011</v>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D114" s="0" t="n">
@@ -3139,16 +3142,16 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>1100005</v>
+        <v>1100001</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D115" s="0" t="n">
@@ -3157,16 +3160,16 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>1100006</v>
+        <v>1100002</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D116" s="0" t="n">
@@ -3175,16 +3178,16 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>1100007</v>
+        <v>1100003</v>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D117" s="0" t="n">
@@ -3193,16 +3196,16 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>1100008</v>
+        <v>1100004</v>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D118" s="0" t="n">
@@ -3211,16 +3214,16 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>1100009</v>
+        <v>1100005</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D119" s="0" t="n">
@@ -3229,16 +3232,16 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>1100010</v>
+        <v>1100006</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D120" s="0" t="n">
@@ -3247,16 +3250,16 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>1100011</v>
+        <v>1100007</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D121" s="0" t="n">
@@ -3265,16 +3268,16 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>1100012</v>
+        <v>1100008</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D122" s="0" t="n">
@@ -3283,16 +3286,16 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>1100013</v>
+        <v>1100009</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D123" s="0" t="n">
@@ -3301,19 +3304,91 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="B124" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_10.wav</t>
+        </is>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐10</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="B125" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_11.mp3</t>
+        </is>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐11</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_12.mp3</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐12</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B127" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B124" s="0" t="inlineStr">
+      <c r="B128" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C124" s="0" t="inlineStr">
+      <c r="C128" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D124" s="0" t="n">
+      <c r="D128" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -2503,6 +2503,9 @@
       <c r="D79" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="E79" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
@@ -2925,20 +2928,20 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" s="0" t="n">
         <v>600003</v>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>sound_magic_3.wav</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>魔法3</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1692,89 +1692,89 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="0" t="n">
-        <v>200001</v>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t>sound_knife_hit_1.wav</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>刀-hit_1</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="n">
+      <c r="A35" t="n">
+        <v>100002</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sound_knife_miss_2.wav</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>刀-miss_2</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="n">
-        <v>200002</v>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>sound_knife_hit_2.wav</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>刀-hit_2</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="n">
+      <c r="A36" t="n">
+        <v>100003</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sound_knife_miss_3.wav</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>刀-miss_3</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="n">
-        <v>200003</v>
-      </c>
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t>sound_knife_hit_3.wav</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>刀-hit_3</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="n">
+      <c r="A37" t="n">
+        <v>100004</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sound_knife_miss_4.wav</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>刀-miss_4</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="n">
-        <v>200004</v>
-      </c>
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>sound_knife_hit_4.wav</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>刀-hit_4</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="n">
+      <c r="A38" t="n">
+        <v>100005</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sound_knife_miss_5.wav</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>刀-miss_5</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="n">
-        <v>200005</v>
+        <v>200001</v>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>sound_knife_hit_5.wav</t>
+          <t>sound_knife_hit_1.wav</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>刀-hit_5</t>
+          <t>刀-hit_1</t>
         </is>
       </c>
       <c r="D39" s="0" t="n">
@@ -1783,16 +1783,16 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="n">
-        <v>200006</v>
+        <v>200002</v>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>sound_knife_hit_6.wav</t>
+          <t>sound_knife_hit_2.wav</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>刀-hit_6</t>
+          <t>刀-hit_2</t>
         </is>
       </c>
       <c r="D40" s="0" t="n">
@@ -1801,16 +1801,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="n">
-        <v>200007</v>
+        <v>200003</v>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>sound_knife_hit_7.wav</t>
+          <t>sound_knife_hit_3.wav</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>刀-hit_7</t>
+          <t>刀-hit_3</t>
         </is>
       </c>
       <c r="D41" s="0" t="n">
@@ -1819,16 +1819,16 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="n">
-        <v>200008</v>
+        <v>200004</v>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>sound_knife_hit_8.wav</t>
+          <t>sound_knife_hit_4.wav</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>刀-hit_8</t>
+          <t>刀-hit_4</t>
         </is>
       </c>
       <c r="D42" s="0" t="n">
@@ -1837,37 +1837,34 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="n">
-        <v>300001</v>
+        <v>200005</v>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>sound_card_1.wav</t>
+          <t>sound_knife_hit_5.wav</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>卡片1</t>
+          <t>刀-hit_5</t>
         </is>
       </c>
       <c r="D43" s="0" t="n">
         <v>0</v>
-      </c>
-      <c r="E43" s="0" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="n">
-        <v>310001</v>
+        <v>200006</v>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>sound_clean_1.wav</t>
+          <t>sound_knife_hit_6.wav</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>清扫1</t>
+          <t>刀-hit_6</t>
         </is>
       </c>
       <c r="D44" s="0" t="n">
@@ -1876,16 +1873,16 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="n">
-        <v>310002</v>
+        <v>200007</v>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>sound_clean_2.wav</t>
+          <t>sound_knife_hit_7.wav</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>清扫2</t>
+          <t>刀-hit_7</t>
         </is>
       </c>
       <c r="D45" s="0" t="n">
@@ -1894,16 +1891,16 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="n">
-        <v>320001</v>
+        <v>200008</v>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>sound_coin_1.wav</t>
+          <t>sound_knife_hit_8.wav</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>金币1</t>
+          <t>刀-hit_8</t>
         </is>
       </c>
       <c r="D46" s="0" t="n">
@@ -1912,268 +1909,271 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="n">
-        <v>330001</v>
+        <v>300001</v>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>sound_cook_1.wav</t>
+          <t>sound_card_1.wav</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>烹饪1</t>
+          <t>卡片1</t>
         </is>
       </c>
       <c r="D47" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="E47" s="0" t="n">
+        <v>1.5</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="0" t="n">
-        <v>340001</v>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>sound_countdown_1.wav</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>倒计时1</t>
-        </is>
-      </c>
-      <c r="D48" s="0" t="n">
+      <c r="A48" t="n">
+        <v>300002</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>sound_card_2.wav</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>卡片2</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="0" t="n">
-        <v>340002</v>
-      </c>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>sound_countdown_2.wav</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>倒计时2</t>
-        </is>
-      </c>
-      <c r="D49" s="0" t="n">
+      <c r="A49" t="n">
+        <v>300003</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sound_card_3.wav</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>卡片3</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="0" t="n">
-        <v>350001</v>
-      </c>
-      <c r="B50" s="0" t="inlineStr">
-        <is>
-          <t>sound_damage_1.wav</t>
-        </is>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>受伤1</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="n">
+      <c r="A50" t="n">
+        <v>300004</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>sound_card_4.wav</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>卡片4</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="0" t="n">
-        <v>360001</v>
-      </c>
-      <c r="B51" s="0" t="inlineStr">
-        <is>
-          <t>sound_dice_1.wav</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>骰子1</t>
-        </is>
-      </c>
-      <c r="D51" s="0" t="n">
+      <c r="A51" t="n">
+        <v>300005</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>sound_card_5.wav</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>卡片5</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="0" t="n">
-        <v>370001</v>
-      </c>
-      <c r="B52" s="0" t="inlineStr">
-        <is>
-          <t>sound_door_1.wav</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>开门1</t>
-        </is>
-      </c>
-      <c r="D52" s="0" t="n">
+      <c r="A52" t="n">
+        <v>300006</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sound_card_6.ogg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>卡片6</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="0" t="n">
-        <v>380001</v>
-      </c>
-      <c r="B53" s="0" t="inlineStr">
-        <is>
-          <t>sound_eat_1.wav</t>
-        </is>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>进食1</t>
-        </is>
-      </c>
-      <c r="D53" s="0" t="n">
+      <c r="A53" t="n">
+        <v>300007</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>sound_card_7.ogg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>卡片7</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="0" t="n">
-        <v>380002</v>
-      </c>
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>sound_eat_2.wav</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>进食2</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="n">
+      <c r="A54" t="n">
+        <v>300008</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sound_card_8.ogg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>卡片8</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="0" t="n">
-        <v>390001</v>
-      </c>
-      <c r="B55" s="0" t="inlineStr">
-        <is>
-          <t>sound_error_1.wav</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>错误1</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="n">
+      <c r="A55" t="n">
+        <v>300009</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>sound_card_9.wav</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>卡片9</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="0" t="n">
-        <v>400001</v>
-      </c>
-      <c r="B56" s="0" t="inlineStr">
-        <is>
-          <t>sound_fight_1.wav</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>战斗1</t>
-        </is>
-      </c>
-      <c r="D56" s="0" t="n">
+      <c r="A56" t="n">
+        <v>300010</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>sound_card_10.ogg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>卡片10</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="0" t="n">
-        <v>400002</v>
-      </c>
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>sound_fight_2.wav</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>战斗2</t>
-        </is>
-      </c>
-      <c r="D57" s="0" t="n">
+      <c r="A57" t="n">
+        <v>300011</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sound_card_11.ogg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>卡片11</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="0" t="n">
-        <v>400003</v>
-      </c>
-      <c r="B58" s="0" t="inlineStr">
-        <is>
-          <t>sound_fight_3.wav</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>战斗3</t>
-        </is>
-      </c>
-      <c r="D58" s="0" t="n">
+      <c r="A58" t="n">
+        <v>300012</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>sound_card_12.ogg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>卡片12</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="0" t="n">
-        <v>410001</v>
-      </c>
-      <c r="B59" s="0" t="inlineStr">
-        <is>
-          <t>sound_firecrackers_1.wav</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>鞭炮1</t>
-        </is>
-      </c>
-      <c r="D59" s="0" t="n">
+      <c r="A59" t="n">
+        <v>300013</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>sound_card_13.ogg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>卡片13</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="0" t="n">
-        <v>420001</v>
-      </c>
-      <c r="B60" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_1.wav</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>打击1</t>
-        </is>
-      </c>
-      <c r="D60" s="0" t="n">
+      <c r="A60" t="n">
+        <v>300014</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>sound_card_14.ogg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>卡片14</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>420002</v>
+        <v>310001</v>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_2.wav</t>
+          <t>sound_clean_1.wav</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>打击2</t>
+          <t>清扫1</t>
         </is>
       </c>
       <c r="D61" s="0" t="n">
@@ -2182,16 +2182,16 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>420003</v>
+        <v>310002</v>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_3.wav</t>
+          <t>sound_clean_2.wav</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>打击3</t>
+          <t>清扫2</t>
         </is>
       </c>
       <c r="D62" s="0" t="n">
@@ -2200,16 +2200,16 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>420004</v>
+        <v>320001</v>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_4.wav</t>
+          <t>sound_coin_1.wav</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>打击4</t>
+          <t>金币1</t>
         </is>
       </c>
       <c r="D63" s="0" t="n">
@@ -2217,269 +2217,269 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="0" t="n">
-        <v>420005</v>
-      </c>
-      <c r="B64" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_5.wav</t>
-        </is>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>打击5</t>
-        </is>
-      </c>
-      <c r="D64" s="0" t="n">
+      <c r="A64" t="n">
+        <v>320002</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>sound_coin_2.wav</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>金币2</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="0" t="n">
-        <v>420006</v>
-      </c>
-      <c r="B65" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_6.wav</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="inlineStr">
-        <is>
-          <t>打击6</t>
-        </is>
-      </c>
-      <c r="D65" s="0" t="n">
+      <c r="A65" t="n">
+        <v>320003</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>sound_coin_3.wav</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>金币3</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="0" t="n">
-        <v>420007</v>
-      </c>
-      <c r="B66" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_7.wav</t>
-        </is>
-      </c>
-      <c r="C66" s="0" t="inlineStr">
-        <is>
-          <t>打击7</t>
-        </is>
-      </c>
-      <c r="D66" s="0" t="n">
+      <c r="A66" t="n">
+        <v>320004</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>sound_coin_4.wav</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>金币4</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="0" t="n">
-        <v>420008</v>
-      </c>
-      <c r="B67" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_8.wav</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>打击8</t>
-        </is>
-      </c>
-      <c r="D67" s="0" t="n">
+      <c r="A67" t="n">
+        <v>320005</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sound_coin_5.wav</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>金币5</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="0" t="n">
-        <v>420009</v>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_9.wav</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>打击9</t>
-        </is>
-      </c>
-      <c r="D68" s="0" t="n">
+      <c r="A68" t="n">
+        <v>320006</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>sound_coin_6.wav</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>金币6</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="0" t="n">
-        <v>420010</v>
-      </c>
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_10.wav</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>打击10</t>
-        </is>
-      </c>
-      <c r="D69" s="0" t="n">
+      <c r="A69" t="n">
+        <v>320007</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>sound_coin_7.wav</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>金币7</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="0" t="n">
-        <v>420011</v>
-      </c>
-      <c r="B70" s="0" t="inlineStr">
-        <is>
-          <t>sound_hit_11.wav</t>
-        </is>
-      </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>打击11</t>
-        </is>
-      </c>
-      <c r="D70" s="0" t="n">
+      <c r="A70" t="n">
+        <v>320008</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>sound_coin_8.wav</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>金币8</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="0" t="n">
-        <v>430001</v>
-      </c>
-      <c r="B71" s="0" t="inlineStr">
-        <is>
-          <t>sound_knock_1.wav</t>
-        </is>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>敲击1</t>
-        </is>
-      </c>
-      <c r="D71" s="0" t="n">
+      <c r="A71" t="n">
+        <v>320009</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>sound_coin_9.ogg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>金币9</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="0" t="n">
-        <v>440001</v>
-      </c>
-      <c r="B72" s="0" t="inlineStr">
-        <is>
-          <t>sound_lock_1.wav</t>
-        </is>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>上锁1</t>
-        </is>
-      </c>
-      <c r="D72" s="0" t="n">
+      <c r="A72" t="n">
+        <v>320010</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>sound_coin_10.ogg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>金币10</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="0" t="n">
-        <v>440002</v>
-      </c>
-      <c r="B73" s="0" t="inlineStr">
-        <is>
-          <t>sound_lock_2.wav</t>
-        </is>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>上锁2</t>
-        </is>
-      </c>
-      <c r="D73" s="0" t="n">
+      <c r="A73" t="n">
+        <v>320011</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sound_coin_11.ogg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>金币11</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="0" t="n">
-        <v>440003</v>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>sound_lock_3.wav</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>上锁3</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="n">
+      <c r="A74" t="n">
+        <v>320012</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>sound_coin_12.ogg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>金币12</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="0" t="n">
-        <v>440004</v>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>sound_lock_4.wav</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>上锁4</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="n">
+      <c r="A75" t="n">
+        <v>320013</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>sound_coin_13.ogg</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>金币13</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="0" t="n">
-        <v>450001</v>
-      </c>
-      <c r="B76" s="0" t="inlineStr">
-        <is>
-          <t>sound_lose_1.wav</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>失败1</t>
-        </is>
-      </c>
-      <c r="D76" s="0" t="n">
+      <c r="A76" t="n">
+        <v>320014</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>sound_coin_14.wav</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>金币14</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="0" t="n">
-        <v>460001</v>
-      </c>
-      <c r="B77" s="0" t="inlineStr">
-        <is>
-          <t>sound_map_1.wav</t>
-        </is>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>地图1</t>
-        </is>
-      </c>
-      <c r="D77" s="0" t="n">
+      <c r="A77" t="n">
+        <v>320015</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>sound_coin_15.wav</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>金币15</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>470001</v>
+        <v>330001</v>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>sound_medicine_1.wav</t>
+          <t>sound_cook_1.wav</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>药剂1</t>
+          <t>烹饪1</t>
         </is>
       </c>
       <c r="D78" s="0" t="n">
@@ -2488,58 +2488,52 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>480001</v>
+        <v>340001</v>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_1.wav</t>
+          <t>sound_countdown_1.wav</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>支付1</t>
+          <t>倒计时1</t>
         </is>
       </c>
       <c r="D79" s="0" t="n">
         <v>0</v>
-      </c>
-      <c r="E79" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>480002</v>
+        <v>340002</v>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_2.wav</t>
+          <t>sound_countdown_2.wav</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>支付2</t>
+          <t>倒计时2</t>
         </is>
       </c>
       <c r="D80" s="0" t="n">
         <v>0</v>
-      </c>
-      <c r="E80" s="0" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>480003</v>
+        <v>350001</v>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_3.wav</t>
+          <t>sound_damage_1.wav</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>支付3</t>
+          <t>受伤1</t>
         </is>
       </c>
       <c r="D81" s="0" t="n">
@@ -2548,16 +2542,16 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>480004</v>
+        <v>360001</v>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_4.wav</t>
+          <t>sound_dice_1.wav</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>支付4</t>
+          <t>骰子1</t>
         </is>
       </c>
       <c r="D82" s="0" t="n">
@@ -2566,16 +2560,16 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>480005</v>
+        <v>370001</v>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_5.wav</t>
+          <t>sound_door_1.wav</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>支付5</t>
+          <t>开门1</t>
         </is>
       </c>
       <c r="D83" s="0" t="n">
@@ -2584,16 +2578,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>480006</v>
+        <v>380001</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_6.wav</t>
+          <t>sound_eat_1.wav</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>支付6</t>
+          <t>进食1</t>
         </is>
       </c>
       <c r="D84" s="0" t="n">
@@ -2602,16 +2596,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>480007</v>
+        <v>380002</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_7.wav</t>
+          <t>sound_eat_2.wav</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>支付7</t>
+          <t>进食2</t>
         </is>
       </c>
       <c r="D85" s="0" t="n">
@@ -2620,16 +2614,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>490001</v>
+        <v>390001</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>sound_reward_1.wav</t>
+          <t>sound_error_1.wav</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>奖励1</t>
+          <t>错误1</t>
         </is>
       </c>
       <c r="D86" s="0" t="n">
@@ -2638,16 +2632,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>490002</v>
+        <v>400001</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>sound_reward_2.wav</t>
+          <t>sound_fight_1.wav</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>奖励2</t>
+          <t>战斗1</t>
         </is>
       </c>
       <c r="D87" s="0" t="n">
@@ -2656,16 +2650,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>490003</v>
+        <v>400002</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>sound_reward_3.wav</t>
+          <t>sound_fight_2.wav</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>奖励3</t>
+          <t>战斗2</t>
         </is>
       </c>
       <c r="D88" s="0" t="n">
@@ -2674,37 +2668,34 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>500001</v>
+        <v>400003</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>sound_set_1.wav</t>
+          <t>sound_fight_3.wav</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>设置1</t>
+          <t>战斗3</t>
         </is>
       </c>
       <c r="D89" s="0" t="n">
         <v>0</v>
-      </c>
-      <c r="E89" s="0" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>510001</v>
+        <v>410001</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>sound_shot_1.wav</t>
+          <t>sound_firecrackers_1.wav</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>射击1</t>
+          <t>鞭炮1</t>
         </is>
       </c>
       <c r="D90" s="0" t="n">
@@ -2713,16 +2704,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>520001</v>
+        <v>420001</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>sound_show_1.wav</t>
+          <t>sound_hit_1.wav</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>展示1</t>
+          <t>打击1</t>
         </is>
       </c>
       <c r="D91" s="0" t="n">
@@ -2731,16 +2722,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>530001</v>
+        <v>420002</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>sound_thunder_1.wav</t>
+          <t>sound_hit_2.wav</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>雷电1</t>
+          <t>打击2</t>
         </is>
       </c>
       <c r="D92" s="0" t="n">
@@ -2749,16 +2740,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>540001</v>
+        <v>420003</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>sound_thunderstorm_1.wav</t>
+          <t>sound_hit_3.wav</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>雷暴1</t>
+          <t>打击3</t>
         </is>
       </c>
       <c r="D93" s="0" t="n">
@@ -2767,16 +2758,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>550001</v>
+        <v>420004</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>sound_time_countdown_1.wav</t>
+          <t>sound_hit_4.wav</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>时间倒计时1</t>
+          <t>打击4</t>
         </is>
       </c>
       <c r="D94" s="0" t="n">
@@ -2785,16 +2776,16 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>560001</v>
+        <v>420005</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>sound_turntable_1.wav</t>
+          <t>sound_hit_5.wav</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>转盘1</t>
+          <t>打击5</t>
         </is>
       </c>
       <c r="D95" s="0" t="n">
@@ -2803,16 +2794,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>570001</v>
+        <v>420006</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>sound_walk_1.wav</t>
+          <t>sound_hit_6.wav</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>行走1</t>
+          <t>打击6</t>
         </is>
       </c>
       <c r="D96" s="0" t="n">
@@ -2821,16 +2812,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>580001</v>
+        <v>420007</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>sound_win_1.wav</t>
+          <t>sound_hit_7.wav</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>胜利1</t>
+          <t>打击7</t>
         </is>
       </c>
       <c r="D97" s="0" t="n">
@@ -2839,16 +2830,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>580003</v>
+        <v>420008</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>sound_win_3.wav</t>
+          <t>sound_hit_8.wav</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>胜利3</t>
+          <t>打击8</t>
         </is>
       </c>
       <c r="D98" s="0" t="n">
@@ -2857,16 +2848,16 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>580004</v>
+        <v>420009</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>sound_win_4.wav</t>
+          <t>sound_hit_9.wav</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>胜利4</t>
+          <t>打击9</t>
         </is>
       </c>
       <c r="D99" s="0" t="n">
@@ -2875,16 +2866,16 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>590001</v>
+        <v>420010</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>sound_continuous_1.wav</t>
+          <t>sound_hit_10.wav</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>持续1</t>
+          <t>打击10</t>
         </is>
       </c>
       <c r="D100" s="0" t="n">
@@ -2893,16 +2884,16 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>600001</v>
+        <v>420011</v>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_1.wav</t>
+          <t>sound_hit_11.wav</t>
         </is>
       </c>
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>魔法1</t>
+          <t>打击11</t>
         </is>
       </c>
       <c r="D101" s="0" t="n">
@@ -2910,488 +2901,1343 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="0" t="n">
-        <v>600002</v>
-      </c>
-      <c r="B102" s="0" t="inlineStr">
-        <is>
-          <t>sound_magic_2.wav</t>
-        </is>
-      </c>
-      <c r="C102" s="0" t="inlineStr">
-        <is>
-          <t>魔法2</t>
-        </is>
-      </c>
-      <c r="D102" s="0" t="n">
+      <c r="A102" t="n">
+        <v>420012</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>sound_hit_12.wav</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>打击12</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="0" t="n">
-        <v>600003</v>
-      </c>
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>sound_magic_3.wav</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>魔法3</t>
-        </is>
-      </c>
-      <c r="D103" s="0" t="n">
+      <c r="A103" t="n">
+        <v>420013</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>sound_hit_13.wav</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>打击13</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
-        <v>1000001</v>
+        <v>430001</v>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>music_fight_1.wav</t>
+          <t>sound_knock_1.wav</t>
         </is>
       </c>
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐1</t>
+          <t>敲击1</t>
         </is>
       </c>
       <c r="D104" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="0" t="n">
-        <v>1000002</v>
-      </c>
-      <c r="B105" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_2.wav</t>
-        </is>
-      </c>
-      <c r="C105" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐2</t>
-        </is>
-      </c>
-      <c r="D105" s="0" t="n">
-        <v>1</v>
+      <c r="A105" t="n">
+        <v>430002</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>sound_knock_2.wav</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>敲击2</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="0" t="n">
-        <v>1000003</v>
-      </c>
-      <c r="B106" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_3.wav</t>
-        </is>
-      </c>
-      <c r="C106" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐3</t>
-        </is>
-      </c>
-      <c r="D106" s="0" t="n">
-        <v>1</v>
+      <c r="A106" t="n">
+        <v>430003</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>sound_knock_3.ogg</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>敲击3</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="0" t="n">
-        <v>1000004</v>
-      </c>
-      <c r="B107" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_4.wav</t>
-        </is>
-      </c>
-      <c r="C107" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐4</t>
-        </is>
-      </c>
-      <c r="D107" s="0" t="n">
-        <v>1</v>
+      <c r="A107" t="n">
+        <v>430004</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>sound_knock_4.ogg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>敲击4</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="0" t="n">
-        <v>1000005</v>
-      </c>
-      <c r="B108" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_5.wav</t>
-        </is>
-      </c>
-      <c r="C108" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐5</t>
-        </is>
-      </c>
-      <c r="D108" s="0" t="n">
-        <v>1</v>
+      <c r="A108" t="n">
+        <v>430005</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>sound_knock_5.ogg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>敲击5</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="0" t="n">
-        <v>1000006</v>
-      </c>
-      <c r="B109" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_6.wav</t>
-        </is>
-      </c>
-      <c r="C109" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐6</t>
-        </is>
-      </c>
-      <c r="D109" s="0" t="n">
-        <v>1</v>
+      <c r="A109" t="n">
+        <v>430006</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>sound_knock_6.wav</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>敲击6</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>1000007</v>
+        <v>440001</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>sound_lock_1.wav</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>上锁1</t>
         </is>
       </c>
       <c r="D110" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>1000008</v>
+        <v>440002</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>sound_lock_2.wav</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>上锁2</t>
         </is>
       </c>
       <c r="D111" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>1000009</v>
+        <v>440003</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>sound_lock_3.wav</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>上锁3</t>
         </is>
       </c>
       <c r="D112" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>1000010</v>
+        <v>440004</v>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>sound_lock_4.wav</t>
         </is>
       </c>
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>上锁4</t>
         </is>
       </c>
       <c r="D113" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="0" t="n">
-        <v>1000011</v>
-      </c>
-      <c r="B114" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_11.mp3</t>
-        </is>
-      </c>
-      <c r="C114" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐11</t>
-        </is>
-      </c>
-      <c r="D114" s="0" t="n">
-        <v>1</v>
+      <c r="A114" t="n">
+        <v>440005</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>sound_lock_5.ogg</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>上锁5</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>1100001</v>
+        <v>450001</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>sound_lose_1.wav</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>失败1</t>
         </is>
       </c>
       <c r="D115" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>1100002</v>
+        <v>460001</v>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>sound_map_1.wav</t>
         </is>
       </c>
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>地图1</t>
         </is>
       </c>
       <c r="D116" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="0" t="n">
-        <v>1100003</v>
-      </c>
-      <c r="B117" s="0" t="inlineStr">
-        <is>
-          <t>music_gaming_3.wav</t>
-        </is>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
-        <is>
-          <t>游戏中音乐3</t>
-        </is>
-      </c>
-      <c r="D117" s="0" t="n">
-        <v>1</v>
+      <c r="A117" t="n">
+        <v>460002</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sound_map_2.ogg</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>地图2</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="0" t="n">
-        <v>1100004</v>
-      </c>
-      <c r="B118" s="0" t="inlineStr">
-        <is>
-          <t>music_gaming_4.wav</t>
-        </is>
-      </c>
-      <c r="C118" s="0" t="inlineStr">
-        <is>
-          <t>游戏中音乐4</t>
-        </is>
-      </c>
-      <c r="D118" s="0" t="n">
-        <v>1</v>
+      <c r="A118" t="n">
+        <v>460003</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>sound_map_3.ogg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>地图3</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>1100005</v>
+        <v>470001</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>sound_medicine_1.wav</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>药剂1</t>
         </is>
       </c>
       <c r="D119" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>1100006</v>
+        <v>480001</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>sound_pay_1.wav</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>支付1</t>
         </is>
       </c>
       <c r="D120" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E120" s="0" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>1100007</v>
+        <v>480002</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>sound_pay_2.wav</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>支付2</t>
         </is>
       </c>
       <c r="D121" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E121" s="0" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>1100008</v>
+        <v>480003</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>sound_pay_3.wav</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>支付3</t>
         </is>
       </c>
       <c r="D122" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>1100009</v>
+        <v>480004</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>sound_pay_4.wav</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>支付4</t>
         </is>
       </c>
       <c r="D123" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>1100010</v>
+        <v>480005</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>sound_pay_5.wav</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>支付5</t>
         </is>
       </c>
       <c r="D124" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>1100011</v>
+        <v>480006</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>sound_pay_6.wav</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>支付6</t>
         </is>
       </c>
       <c r="D125" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>1100012</v>
+        <v>480007</v>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>sound_pay_7.wav</t>
         </is>
       </c>
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>支付7</t>
         </is>
       </c>
       <c r="D126" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="0" t="n">
-        <v>1100013</v>
-      </c>
-      <c r="B127" s="0" t="inlineStr">
-        <is>
-          <t>music_gaming_13.mp3</t>
-        </is>
-      </c>
-      <c r="C127" s="0" t="inlineStr">
-        <is>
-          <t>游戏中音乐13</t>
-        </is>
-      </c>
-      <c r="D127" s="0" t="n">
-        <v>1</v>
+      <c r="A127" t="n">
+        <v>480008</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>sound_pay_8.wav</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>支付8</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
+        <v>490001</v>
+      </c>
+      <c r="B128" s="0" t="inlineStr">
+        <is>
+          <t>sound_reward_1.wav</t>
+        </is>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>奖励1</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="n">
+        <v>490002</v>
+      </c>
+      <c r="B129" s="0" t="inlineStr">
+        <is>
+          <t>sound_reward_2.wav</t>
+        </is>
+      </c>
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>奖励2</t>
+        </is>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="n">
+        <v>490003</v>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t>sound_reward_3.wav</t>
+        </is>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>奖励3</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>490004</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>sound_reward_4.wav</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>奖励4</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>490005</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>sound_reward_5.wav</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>奖励5</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>490006</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>sound_reward_6.wav</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>奖励6</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>sound_set_1.wav</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>设置1</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="0" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>500002</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>sound_set_2.wav</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>设置2</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>500003</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>sound_set_3.wav</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>设置3</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="n">
+        <v>510001</v>
+      </c>
+      <c r="B137" s="0" t="inlineStr">
+        <is>
+          <t>sound_shot_1.wav</t>
+        </is>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>射击1</t>
+        </is>
+      </c>
+      <c r="D137" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="n">
+        <v>520001</v>
+      </c>
+      <c r="B138" s="0" t="inlineStr">
+        <is>
+          <t>sound_show_1.wav</t>
+        </is>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>展示1</t>
+        </is>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="n">
+        <v>530001</v>
+      </c>
+      <c r="B139" s="0" t="inlineStr">
+        <is>
+          <t>sound_thunder_1.wav</t>
+        </is>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>雷电1</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0" t="n">
+        <v>540001</v>
+      </c>
+      <c r="B140" s="0" t="inlineStr">
+        <is>
+          <t>sound_thunderstorm_1.wav</t>
+        </is>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>雷暴1</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0" t="n">
+        <v>550001</v>
+      </c>
+      <c r="B141" s="0" t="inlineStr">
+        <is>
+          <t>sound_time_countdown_1.wav</t>
+        </is>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>时间倒计时1</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0" t="n">
+        <v>560001</v>
+      </c>
+      <c r="B142" s="0" t="inlineStr">
+        <is>
+          <t>sound_turntable_1.wav</t>
+        </is>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>转盘1</t>
+        </is>
+      </c>
+      <c r="D142" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0" t="n">
+        <v>570001</v>
+      </c>
+      <c r="B143" s="0" t="inlineStr">
+        <is>
+          <t>sound_walk_1.wav</t>
+        </is>
+      </c>
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>行走1</t>
+        </is>
+      </c>
+      <c r="D143" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0" t="n">
+        <v>580001</v>
+      </c>
+      <c r="B144" s="0" t="inlineStr">
+        <is>
+          <t>sound_win_1.wav</t>
+        </is>
+      </c>
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>胜利1</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0" t="n">
+        <v>580003</v>
+      </c>
+      <c r="B145" s="0" t="inlineStr">
+        <is>
+          <t>sound_win_3.wav</t>
+        </is>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>胜利3</t>
+        </is>
+      </c>
+      <c r="D145" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0" t="n">
+        <v>580004</v>
+      </c>
+      <c r="B146" s="0" t="inlineStr">
+        <is>
+          <t>sound_win_4.wav</t>
+        </is>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>胜利4</t>
+        </is>
+      </c>
+      <c r="D146" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0" t="n">
+        <v>590001</v>
+      </c>
+      <c r="B147" s="0" t="inlineStr">
+        <is>
+          <t>sound_continuous_1.wav</t>
+        </is>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>持续1</t>
+        </is>
+      </c>
+      <c r="D147" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0" t="n">
+        <v>600001</v>
+      </c>
+      <c r="B148" s="0" t="inlineStr">
+        <is>
+          <t>sound_magic_1.wav</t>
+        </is>
+      </c>
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>魔法1</t>
+        </is>
+      </c>
+      <c r="D148" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0" t="n">
+        <v>600002</v>
+      </c>
+      <c r="B149" s="0" t="inlineStr">
+        <is>
+          <t>sound_magic_2.wav</t>
+        </is>
+      </c>
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>魔法2</t>
+        </is>
+      </c>
+      <c r="D149" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0" t="n">
+        <v>600003</v>
+      </c>
+      <c r="B150" s="0" t="inlineStr">
+        <is>
+          <t>sound_magic_3.wav</t>
+        </is>
+      </c>
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>魔法3</t>
+        </is>
+      </c>
+      <c r="D150" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0" t="n">
+        <v>1000001</v>
+      </c>
+      <c r="B151" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_1.wav</t>
+        </is>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐1</t>
+        </is>
+      </c>
+      <c r="D151" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0" t="n">
+        <v>1000002</v>
+      </c>
+      <c r="B152" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_2.wav</t>
+        </is>
+      </c>
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐2</t>
+        </is>
+      </c>
+      <c r="D152" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0" t="n">
+        <v>1000003</v>
+      </c>
+      <c r="B153" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_3.wav</t>
+        </is>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐3</t>
+        </is>
+      </c>
+      <c r="D153" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0" t="n">
+        <v>1000004</v>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_4.wav</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐4</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0" t="n">
+        <v>1000005</v>
+      </c>
+      <c r="B155" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_5.wav</t>
+        </is>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐5</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0" t="n">
+        <v>1000006</v>
+      </c>
+      <c r="B156" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_6.wav</t>
+        </is>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐6</t>
+        </is>
+      </c>
+      <c r="D156" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0" t="n">
+        <v>1000007</v>
+      </c>
+      <c r="B157" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_7.wav</t>
+        </is>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐7</t>
+        </is>
+      </c>
+      <c r="D157" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0" t="n">
+        <v>1000008</v>
+      </c>
+      <c r="B158" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_8.wav</t>
+        </is>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐8</t>
+        </is>
+      </c>
+      <c r="D158" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0" t="n">
+        <v>1000009</v>
+      </c>
+      <c r="B159" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_9.mp3</t>
+        </is>
+      </c>
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐9</t>
+        </is>
+      </c>
+      <c r="D159" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0" t="n">
+        <v>1000010</v>
+      </c>
+      <c r="B160" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_10.mp3</t>
+        </is>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐10</t>
+        </is>
+      </c>
+      <c r="D160" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0" t="n">
+        <v>1000011</v>
+      </c>
+      <c r="B161" s="0" t="inlineStr">
+        <is>
+          <t>music_fight_11.mp3</t>
+        </is>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>战斗音乐11</t>
+        </is>
+      </c>
+      <c r="D161" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0" t="n">
+        <v>1100001</v>
+      </c>
+      <c r="B162" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_1.wav</t>
+        </is>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐1</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0" t="n">
+        <v>1100002</v>
+      </c>
+      <c r="B163" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_2.wav</t>
+        </is>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐2</t>
+        </is>
+      </c>
+      <c r="D163" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0" t="n">
+        <v>1100003</v>
+      </c>
+      <c r="B164" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_3.wav</t>
+        </is>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐3</t>
+        </is>
+      </c>
+      <c r="D164" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0" t="n">
+        <v>1100004</v>
+      </c>
+      <c r="B165" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_4.wav</t>
+        </is>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐4</t>
+        </is>
+      </c>
+      <c r="D165" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0" t="n">
+        <v>1100005</v>
+      </c>
+      <c r="B166" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_5.wav</t>
+        </is>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐5</t>
+        </is>
+      </c>
+      <c r="D166" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0" t="n">
+        <v>1100006</v>
+      </c>
+      <c r="B167" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_6.wav</t>
+        </is>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐6</t>
+        </is>
+      </c>
+      <c r="D167" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0" t="n">
+        <v>1100007</v>
+      </c>
+      <c r="B168" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_7.wav</t>
+        </is>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐7</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0" t="n">
+        <v>1100008</v>
+      </c>
+      <c r="B169" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_8.wav</t>
+        </is>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐8</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0" t="n">
+        <v>1100009</v>
+      </c>
+      <c r="B170" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_9.wav</t>
+        </is>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐9</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="B171" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_10.wav</t>
+        </is>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐10</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="B172" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_11.mp3</t>
+        </is>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐11</t>
+        </is>
+      </c>
+      <c r="D172" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="B173" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_12.mp3</t>
+        </is>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐12</t>
+        </is>
+      </c>
+      <c r="D173" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B174" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D174" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B128" s="0" t="inlineStr">
+      <c r="B175" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C128" s="0" t="inlineStr">
+      <c r="C175" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D128" s="0" t="n">
+      <c r="D175" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -1692,74 +1692,74 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="0" t="n">
         <v>100002</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>sound_knife_miss_2.wav</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>刀-miss_2</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="0" t="n">
         <v>100003</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>sound_knife_miss_3.wav</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>刀-miss_3</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="0" t="n">
         <v>100004</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>sound_knife_miss_4.wav</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>刀-miss_4</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="0" t="n">
         <v>100005</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>sound_knife_miss_5.wav</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>刀-miss_5</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1929,236 +1929,236 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>300002</v>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>sound_card_2.wav</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>卡片2</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="0" t="n">
         <v>300003</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>sound_card_3.wav</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>卡片3</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="0" t="n">
         <v>300004</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>sound_card_4.wav</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>卡片4</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="0" t="n">
         <v>300005</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>sound_card_5.wav</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>卡片5</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="0" t="n">
         <v>300006</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>sound_card_6.ogg</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>卡片6</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="0" t="n">
         <v>300007</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>sound_card_7.ogg</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>卡片7</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="0" t="n">
         <v>300008</v>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>sound_card_8.ogg</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>卡片8</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="0" t="n">
         <v>300009</v>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>sound_card_9.wav</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>卡片9</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="0" t="n">
         <v>300010</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>sound_card_10.ogg</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>卡片10</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="0" t="n">
         <v>300011</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>sound_card_11.ogg</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>卡片11</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="0" t="n">
         <v>300012</v>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>sound_card_12.ogg</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>卡片12</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="0" t="n">
         <v>300013</v>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>sound_card_13.ogg</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>卡片13</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="0" t="n">
         <v>300014</v>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>sound_card_14.ogg</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>卡片14</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2217,254 +2217,254 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="0" t="n">
         <v>320002</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>sound_coin_2.wav</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>金币2</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="0" t="n">
         <v>320003</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>sound_coin_3.wav</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>金币3</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="0" t="n">
         <v>320004</v>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>sound_coin_4.wav</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>金币4</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="0" t="n">
         <v>320005</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>sound_coin_5.wav</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>金币5</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="0" t="n">
         <v>320006</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>sound_coin_6.wav</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>金币6</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="0" t="n">
         <v>320007</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>sound_coin_7.wav</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>金币7</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="0" t="n">
         <v>320008</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>sound_coin_8.wav</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>金币8</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="0" t="n">
         <v>320009</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>sound_coin_9.ogg</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>金币9</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="0" t="n">
         <v>320010</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>sound_coin_10.ogg</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>金币10</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="0" t="n">
         <v>320011</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>sound_coin_11.ogg</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>金币11</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="0" t="n">
         <v>320012</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>sound_coin_12.ogg</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>金币12</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="0" t="n">
         <v>320013</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>sound_coin_13.ogg</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>金币13</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="0" t="n">
         <v>320014</v>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>sound_coin_14.wav</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>金币14</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="0" t="n">
         <v>320015</v>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>sound_coin_15.wav</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>金币15</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2578,16 +2578,16 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>380001</v>
+        <v>370002</v>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>sound_eat_1.wav</t>
+          <t>sound_door_2.wav</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>进食1</t>
+          <t>开门2</t>
         </is>
       </c>
       <c r="D84" s="0" t="n">
@@ -2596,16 +2596,16 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>380002</v>
+        <v>380001</v>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>sound_eat_2.wav</t>
+          <t>sound_eat_1.wav</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>进食2</t>
+          <t>进食1</t>
         </is>
       </c>
       <c r="D85" s="0" t="n">
@@ -2614,16 +2614,16 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>390001</v>
+        <v>380002</v>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>sound_error_1.wav</t>
+          <t>sound_eat_2.wav</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>错误1</t>
+          <t>进食2</t>
         </is>
       </c>
       <c r="D86" s="0" t="n">
@@ -2632,16 +2632,16 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>400001</v>
+        <v>390001</v>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>sound_fight_1.wav</t>
+          <t>sound_error_1.wav</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>战斗1</t>
+          <t>错误1</t>
         </is>
       </c>
       <c r="D87" s="0" t="n">
@@ -2650,16 +2650,16 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>400002</v>
+        <v>400001</v>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>sound_fight_2.wav</t>
+          <t>sound_fight_1.wav</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>战斗2</t>
+          <t>战斗1</t>
         </is>
       </c>
       <c r="D88" s="0" t="n">
@@ -2668,16 +2668,16 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>400003</v>
+        <v>400002</v>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>sound_fight_3.wav</t>
+          <t>sound_fight_2.wav</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>战斗3</t>
+          <t>战斗2</t>
         </is>
       </c>
       <c r="D89" s="0" t="n">
@@ -2686,16 +2686,16 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>410001</v>
+        <v>400003</v>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>sound_firecrackers_1.wav</t>
+          <t>sound_fight_3.wav</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>鞭炮1</t>
+          <t>战斗3</t>
         </is>
       </c>
       <c r="D90" s="0" t="n">
@@ -2704,16 +2704,16 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>420001</v>
+        <v>410001</v>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_1.wav</t>
+          <t>sound_firecrackers_1.wav</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>打击1</t>
+          <t>鞭炮1</t>
         </is>
       </c>
       <c r="D91" s="0" t="n">
@@ -2722,16 +2722,16 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>420002</v>
+        <v>420001</v>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_2.wav</t>
+          <t>sound_hit_1.wav</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>打击2</t>
+          <t>打击1</t>
         </is>
       </c>
       <c r="D92" s="0" t="n">
@@ -2740,16 +2740,16 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>420003</v>
+        <v>420002</v>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_3.wav</t>
+          <t>sound_hit_2.wav</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>打击3</t>
+          <t>打击2</t>
         </is>
       </c>
       <c r="D93" s="0" t="n">
@@ -2758,16 +2758,16 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>420004</v>
+        <v>420003</v>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_4.wav</t>
+          <t>sound_hit_3.wav</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>打击4</t>
+          <t>打击3</t>
         </is>
       </c>
       <c r="D94" s="0" t="n">
@@ -2776,16 +2776,16 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>420005</v>
+        <v>420004</v>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_5.wav</t>
+          <t>sound_hit_4.wav</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>打击5</t>
+          <t>打击4</t>
         </is>
       </c>
       <c r="D95" s="0" t="n">
@@ -2794,16 +2794,16 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>420006</v>
+        <v>420005</v>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_6.wav</t>
+          <t>sound_hit_5.wav</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>打击6</t>
+          <t>打击5</t>
         </is>
       </c>
       <c r="D96" s="0" t="n">
@@ -2812,16 +2812,16 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>420007</v>
+        <v>420006</v>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_7.wav</t>
+          <t>sound_hit_6.wav</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>打击7</t>
+          <t>打击6</t>
         </is>
       </c>
       <c r="D97" s="0" t="n">
@@ -2830,16 +2830,16 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>420008</v>
+        <v>420007</v>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_8.wav</t>
+          <t>sound_hit_7.wav</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>打击8</t>
+          <t>打击7</t>
         </is>
       </c>
       <c r="D98" s="0" t="n">
@@ -2848,16 +2848,16 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>420009</v>
+        <v>420008</v>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_9.wav</t>
+          <t>sound_hit_8.wav</t>
         </is>
       </c>
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>打击9</t>
+          <t>打击8</t>
         </is>
       </c>
       <c r="D99" s="0" t="n">
@@ -2866,16 +2866,16 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>420010</v>
+        <v>420009</v>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>sound_hit_10.wav</t>
+          <t>sound_hit_9.wav</t>
         </is>
       </c>
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>打击10</t>
+          <t>打击9</t>
         </is>
       </c>
       <c r="D100" s="0" t="n">
@@ -2884,178 +2884,178 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
+        <v>420010</v>
+      </c>
+      <c r="B101" s="0" t="inlineStr">
+        <is>
+          <t>sound_hit_10.wav</t>
+        </is>
+      </c>
+      <c r="C101" s="0" t="inlineStr">
+        <is>
+          <t>打击10</t>
+        </is>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="n">
         <v>420011</v>
       </c>
-      <c r="B101" s="0" t="inlineStr">
+      <c r="B102" s="0" t="inlineStr">
         <is>
           <t>sound_hit_11.wav</t>
         </is>
       </c>
-      <c r="C101" s="0" t="inlineStr">
+      <c r="C102" s="0" t="inlineStr">
         <is>
           <t>打击11</t>
         </is>
       </c>
-      <c r="D101" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
+      <c r="D102" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0" t="n">
         <v>420012</v>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" s="0" t="inlineStr">
         <is>
           <t>sound_hit_12.wav</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" s="0" t="inlineStr">
         <is>
           <t>打击12</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
-        <v>420013</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>sound_hit_13.wav</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>打击13</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="n">
+        <v>420013</v>
+      </c>
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>sound_hit_13.wav</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>打击13</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0" t="n">
         <v>430001</v>
       </c>
-      <c r="B104" s="0" t="inlineStr">
+      <c r="B105" s="0" t="inlineStr">
         <is>
           <t>sound_knock_1.wav</t>
         </is>
       </c>
-      <c r="C104" s="0" t="inlineStr">
+      <c r="C105" s="0" t="inlineStr">
         <is>
           <t>敲击1</t>
         </is>
       </c>
-      <c r="D104" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
+      <c r="D105" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0" t="n">
         <v>430002</v>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" s="0" t="inlineStr">
         <is>
           <t>sound_knock_2.wav</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" s="0" t="inlineStr">
         <is>
           <t>敲击2</t>
         </is>
       </c>
-      <c r="D105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
+      <c r="D106" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0" t="n">
         <v>430003</v>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" s="0" t="inlineStr">
         <is>
           <t>sound_knock_3.ogg</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" s="0" t="inlineStr">
         <is>
           <t>敲击3</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
+      <c r="D107" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0" t="n">
         <v>430004</v>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B108" s="0" t="inlineStr">
         <is>
           <t>sound_knock_4.ogg</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C108" s="0" t="inlineStr">
         <is>
           <t>敲击4</t>
         </is>
       </c>
-      <c r="D107" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
+      <c r="D108" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0" t="n">
         <v>430005</v>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B109" s="0" t="inlineStr">
         <is>
           <t>sound_knock_5.ogg</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C109" s="0" t="inlineStr">
         <is>
           <t>敲击5</t>
         </is>
       </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>430006</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>sound_knock_6.wav</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>敲击6</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="n">
-        <v>440001</v>
+        <v>430006</v>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>sound_lock_1.wav</t>
+          <t>sound_knock_6.wav</t>
         </is>
       </c>
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>上锁1</t>
+          <t>敲击6</t>
         </is>
       </c>
       <c r="D110" s="0" t="n">
@@ -3064,16 +3064,16 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="n">
-        <v>440002</v>
+        <v>440001</v>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>sound_lock_2.wav</t>
+          <t>sound_lock_1.wav</t>
         </is>
       </c>
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>上锁2</t>
+          <t>上锁1</t>
         </is>
       </c>
       <c r="D111" s="0" t="n">
@@ -3082,16 +3082,16 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>440003</v>
+        <v>440002</v>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>sound_lock_3.wav</t>
+          <t>sound_lock_2.wav</t>
         </is>
       </c>
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>上锁3</t>
+          <t>上锁2</t>
         </is>
       </c>
       <c r="D112" s="0" t="n">
@@ -3100,52 +3100,52 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
+        <v>440003</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr">
+        <is>
+          <t>sound_lock_3.wav</t>
+        </is>
+      </c>
+      <c r="C113" s="0" t="inlineStr">
+        <is>
+          <t>上锁3</t>
+        </is>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="n">
         <v>440004</v>
       </c>
-      <c r="B113" s="0" t="inlineStr">
+      <c r="B114" s="0" t="inlineStr">
         <is>
           <t>sound_lock_4.wav</t>
         </is>
       </c>
-      <c r="C113" s="0" t="inlineStr">
+      <c r="C114" s="0" t="inlineStr">
         <is>
           <t>上锁4</t>
         </is>
       </c>
-      <c r="D113" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>440005</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>sound_lock_5.ogg</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>上锁5</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
+      <c r="D114" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>450001</v>
+        <v>440005</v>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>sound_lose_1.wav</t>
+          <t>sound_lock_5.ogg</t>
         </is>
       </c>
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>失败1</t>
+          <t>上锁5</t>
         </is>
       </c>
       <c r="D115" s="0" t="n">
@@ -3154,70 +3154,70 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
+        <v>450001</v>
+      </c>
+      <c r="B116" s="0" t="inlineStr">
+        <is>
+          <t>sound_lose_1.wav</t>
+        </is>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>失败1</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="n">
         <v>460001</v>
       </c>
-      <c r="B116" s="0" t="inlineStr">
+      <c r="B117" s="0" t="inlineStr">
         <is>
           <t>sound_map_1.wav</t>
         </is>
       </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="C117" s="0" t="inlineStr">
         <is>
           <t>地图1</t>
         </is>
       </c>
-      <c r="D116" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
+      <c r="D117" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="n">
         <v>460002</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B118" s="0" t="inlineStr">
         <is>
           <t>sound_map_2.ogg</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C118" s="0" t="inlineStr">
         <is>
           <t>地图2</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>460003</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>sound_map_3.ogg</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>地图3</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
+      <c r="D118" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>470001</v>
+        <v>460003</v>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>sound_medicine_1.wav</t>
+          <t>sound_map_3.ogg</t>
         </is>
       </c>
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>药剂1</t>
+          <t>地图3</t>
         </is>
       </c>
       <c r="D119" s="0" t="n">
@@ -3226,37 +3226,34 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>480001</v>
+        <v>470001</v>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_1.wav</t>
+          <t>sound_medicine_1.wav</t>
         </is>
       </c>
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>支付1</t>
+          <t>药剂1</t>
         </is>
       </c>
       <c r="D120" s="0" t="n">
         <v>0</v>
-      </c>
-      <c r="E120" s="0" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>480002</v>
+        <v>480001</v>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_2.wav</t>
+          <t>sound_pay_1.wav</t>
         </is>
       </c>
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>支付2</t>
+          <t>支付1</t>
         </is>
       </c>
       <c r="D121" s="0" t="n">
@@ -3268,34 +3265,37 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>480003</v>
+        <v>480002</v>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_3.wav</t>
+          <t>sound_pay_2.wav</t>
         </is>
       </c>
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>支付3</t>
+          <t>支付2</t>
         </is>
       </c>
       <c r="D122" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="E122" s="0" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>480004</v>
+        <v>480003</v>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_4.wav</t>
+          <t>sound_pay_3.wav</t>
         </is>
       </c>
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>支付4</t>
+          <t>支付3</t>
         </is>
       </c>
       <c r="D123" s="0" t="n">
@@ -3304,16 +3304,16 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>480005</v>
+        <v>480004</v>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_5.wav</t>
+          <t>sound_pay_4.wav</t>
         </is>
       </c>
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>支付5</t>
+          <t>支付4</t>
         </is>
       </c>
       <c r="D124" s="0" t="n">
@@ -3322,16 +3322,16 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>480006</v>
+        <v>480005</v>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>sound_pay_6.wav</t>
+          <t>sound_pay_5.wav</t>
         </is>
       </c>
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>支付6</t>
+          <t>支付5</t>
         </is>
       </c>
       <c r="D125" s="0" t="n">
@@ -3340,52 +3340,52 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
+        <v>480006</v>
+      </c>
+      <c r="B126" s="0" t="inlineStr">
+        <is>
+          <t>sound_pay_6.wav</t>
+        </is>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>支付6</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="n">
         <v>480007</v>
       </c>
-      <c r="B126" s="0" t="inlineStr">
+      <c r="B127" s="0" t="inlineStr">
         <is>
           <t>sound_pay_7.wav</t>
         </is>
       </c>
-      <c r="C126" s="0" t="inlineStr">
+      <c r="C127" s="0" t="inlineStr">
         <is>
           <t>支付7</t>
         </is>
       </c>
-      <c r="D126" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>480008</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>sound_pay_8.wav</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>支付8</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>490001</v>
+        <v>480008</v>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>sound_reward_1.wav</t>
+          <t>sound_pay_8.wav</t>
         </is>
       </c>
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>奖励1</t>
+          <t>支付8</t>
         </is>
       </c>
       <c r="D128" s="0" t="n">
@@ -3394,16 +3394,16 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>490002</v>
+        <v>490001</v>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>sound_reward_2.wav</t>
+          <t>sound_reward_1.wav</t>
         </is>
       </c>
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>奖励2</t>
+          <t>奖励1</t>
         </is>
       </c>
       <c r="D129" s="0" t="n">
@@ -3412,145 +3412,145 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
+        <v>490002</v>
+      </c>
+      <c r="B130" s="0" t="inlineStr">
+        <is>
+          <t>sound_reward_2.wav</t>
+        </is>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>奖励2</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="n">
         <v>490003</v>
       </c>
-      <c r="B130" s="0" t="inlineStr">
+      <c r="B131" s="0" t="inlineStr">
         <is>
           <t>sound_reward_3.wav</t>
         </is>
       </c>
-      <c r="C130" s="0" t="inlineStr">
+      <c r="C131" s="0" t="inlineStr">
         <is>
           <t>奖励3</t>
         </is>
       </c>
-      <c r="D130" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
+      <c r="D131" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="n">
         <v>490004</v>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" s="0" t="inlineStr">
         <is>
           <t>sound_reward_4.wav</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C132" s="0" t="inlineStr">
         <is>
           <t>奖励4</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
+      <c r="D132" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="n">
         <v>490005</v>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" s="0" t="inlineStr">
         <is>
           <t>sound_reward_5.wav</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C133" s="0" t="inlineStr">
         <is>
           <t>奖励5</t>
         </is>
       </c>
-      <c r="D132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>490006</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>sound_reward_6.wav</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>奖励6</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
+      <c r="D133" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
+        <v>490006</v>
+      </c>
+      <c r="B134" s="0" t="inlineStr">
+        <is>
+          <t>sound_reward_6.wav</t>
+        </is>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>奖励6</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="n">
         <v>500001</v>
       </c>
-      <c r="B134" s="0" t="inlineStr">
+      <c r="B135" s="0" t="inlineStr">
         <is>
           <t>sound_set_1.wav</t>
         </is>
       </c>
-      <c r="C134" s="0" t="inlineStr">
+      <c r="C135" s="0" t="inlineStr">
         <is>
           <t>设置1</t>
         </is>
       </c>
-      <c r="D134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" s="0" t="n">
+      <c r="D135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="0" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
+    <row r="136">
+      <c r="A136" s="0" t="n">
         <v>500002</v>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" s="0" t="inlineStr">
         <is>
           <t>sound_set_2.wav</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C136" s="0" t="inlineStr">
         <is>
           <t>设置2</t>
         </is>
       </c>
-      <c r="D135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>500003</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>sound_set_3.wav</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>设置3</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
+      <c r="D136" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>510001</v>
+        <v>500003</v>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>sound_shot_1.wav</t>
+          <t>sound_set_3.wav</t>
         </is>
       </c>
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>射击1</t>
+          <t>设置3</t>
         </is>
       </c>
       <c r="D137" s="0" t="n">
@@ -3559,16 +3559,16 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>520001</v>
+        <v>510001</v>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>sound_show_1.wav</t>
+          <t>sound_shot_1.wav</t>
         </is>
       </c>
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>展示1</t>
+          <t>射击1</t>
         </is>
       </c>
       <c r="D138" s="0" t="n">
@@ -3577,16 +3577,16 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="n">
-        <v>530001</v>
+        <v>520001</v>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>sound_thunder_1.wav</t>
+          <t>sound_show_1.wav</t>
         </is>
       </c>
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>雷电1</t>
+          <t>展示1</t>
         </is>
       </c>
       <c r="D139" s="0" t="n">
@@ -3595,16 +3595,16 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>540001</v>
+        <v>530001</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>sound_thunderstorm_1.wav</t>
+          <t>sound_thunder_1.wav</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>雷暴1</t>
+          <t>雷电1</t>
         </is>
       </c>
       <c r="D140" s="0" t="n">
@@ -3613,16 +3613,16 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="n">
-        <v>550001</v>
+        <v>540001</v>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>sound_time_countdown_1.wav</t>
+          <t>sound_thunderstorm_1.wav</t>
         </is>
       </c>
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>时间倒计时1</t>
+          <t>雷暴1</t>
         </is>
       </c>
       <c r="D141" s="0" t="n">
@@ -3631,16 +3631,16 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>560001</v>
+        <v>550001</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>sound_turntable_1.wav</t>
+          <t>sound_time_countdown_1.wav</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>转盘1</t>
+          <t>时间倒计时1</t>
         </is>
       </c>
       <c r="D142" s="0" t="n">
@@ -3649,16 +3649,16 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>570001</v>
+        <v>560001</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>sound_walk_1.wav</t>
+          <t>sound_turntable_1.wav</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>行走1</t>
+          <t>转盘1</t>
         </is>
       </c>
       <c r="D143" s="0" t="n">
@@ -3667,16 +3667,16 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>580001</v>
+        <v>570001</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>sound_win_1.wav</t>
+          <t>sound_walk_1.wav</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>胜利1</t>
+          <t>行走1</t>
         </is>
       </c>
       <c r="D144" s="0" t="n">
@@ -3685,16 +3685,16 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>580003</v>
+        <v>580001</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>sound_win_3.wav</t>
+          <t>sound_win_1.wav</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>胜利3</t>
+          <t>胜利1</t>
         </is>
       </c>
       <c r="D145" s="0" t="n">
@@ -3703,16 +3703,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>580004</v>
+        <v>580003</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>sound_win_4.wav</t>
+          <t>sound_win_3.wav</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>胜利4</t>
+          <t>胜利3</t>
         </is>
       </c>
       <c r="D146" s="0" t="n">
@@ -3721,16 +3721,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>590001</v>
+        <v>580004</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>sound_continuous_1.wav</t>
+          <t>sound_win_4.wav</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>持续1</t>
+          <t>胜利4</t>
         </is>
       </c>
       <c r="D147" s="0" t="n">
@@ -3739,16 +3739,16 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>600001</v>
+        <v>590001</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_1.wav</t>
+          <t>sound_continuous_1.wav</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>魔法1</t>
+          <t>持续1</t>
         </is>
       </c>
       <c r="D148" s="0" t="n">
@@ -3757,16 +3757,16 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>600002</v>
+        <v>600001</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_2.wav</t>
+          <t>sound_magic_1.wav</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>魔法2</t>
+          <t>魔法1</t>
         </is>
       </c>
       <c r="D149" s="0" t="n">
@@ -3775,16 +3775,16 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>600003</v>
+        <v>600002</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_3.wav</t>
+          <t>sound_magic_2.wav</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>魔法3</t>
+          <t>魔法2</t>
         </is>
       </c>
       <c r="D150" s="0" t="n">
@@ -3793,70 +3793,70 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>1000001</v>
+        <v>600003</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>music_fight_1.wav</t>
+          <t>sound_magic_3.wav</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐1</t>
+          <t>魔法3</t>
         </is>
       </c>
       <c r="D151" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>1000002</v>
+        <v>610001</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>sound_building_1.wav</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>建造1</t>
         </is>
       </c>
       <c r="D152" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="0" t="n">
-        <v>1000003</v>
-      </c>
-      <c r="B153" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_3.wav</t>
-        </is>
-      </c>
-      <c r="C153" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐3</t>
-        </is>
-      </c>
-      <c r="D153" s="0" t="n">
-        <v>1</v>
+      <c r="A153" t="n">
+        <v>610002</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>sound_building_2.wav</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>建造2</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="n">
-        <v>1000004</v>
+        <v>1000001</v>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>music_fight_4.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐4</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D154" s="0" t="n">
@@ -3865,16 +3865,16 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>1000005</v>
+        <v>1000002</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D155" s="0" t="n">
@@ -3883,16 +3883,16 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1000006</v>
+        <v>1000003</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D156" s="0" t="n">
@@ -3901,16 +3901,16 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1000007</v>
+        <v>1000004</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D157" s="0" t="n">
@@ -3919,16 +3919,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1000008</v>
+        <v>1000005</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D158" s="0" t="n">
@@ -3937,16 +3937,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1000009</v>
+        <v>1000006</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D159" s="0" t="n">
@@ -3955,16 +3955,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1000010</v>
+        <v>1000007</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D160" s="0" t="n">
@@ -3973,16 +3973,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1000011</v>
+        <v>1000008</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D161" s="0" t="n">
@@ -3991,16 +3991,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1100001</v>
+        <v>1000009</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D162" s="0" t="n">
@@ -4009,16 +4009,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1100002</v>
+        <v>1000010</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -4027,16 +4027,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1100003</v>
+        <v>1000011</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -4045,16 +4045,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1100004</v>
+        <v>1100001</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -4063,16 +4063,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1100005</v>
+        <v>1100002</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -4081,16 +4081,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1100006</v>
+        <v>1100003</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -4099,16 +4099,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1100007</v>
+        <v>1100004</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -4117,16 +4117,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1100008</v>
+        <v>1100005</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
@@ -4135,16 +4135,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1100009</v>
+        <v>1100006</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -4153,16 +4153,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1100010</v>
+        <v>1100007</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -4171,16 +4171,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1100011</v>
+        <v>1100008</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -4189,16 +4189,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1100012</v>
+        <v>1100009</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D173" s="0" t="n">
@@ -4207,16 +4207,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1100013</v>
+        <v>1100010</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_10.wav</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐10</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -4225,19 +4225,73 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="B175" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_11.mp3</t>
+        </is>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐11</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="B176" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_12.mp3</t>
+        </is>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐12</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B177" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B175" s="0" t="inlineStr">
+      <c r="B178" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C175" s="0" t="inlineStr">
+      <c r="C178" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D175" s="0" t="n">
+      <c r="D178" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -3828,53 +3828,53 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" s="0" t="n">
         <v>610002</v>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="0" t="inlineStr">
         <is>
           <t>sound_building_2.wav</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C153" s="0" t="inlineStr">
         <is>
           <t>建造2</t>
         </is>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="B154" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_1.wav</t>
-        </is>
-      </c>
-      <c r="C154" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐1</t>
-        </is>
-      </c>
-      <c r="D154" s="0" t="n">
-        <v>1</v>
+      <c r="A154" t="n">
+        <v>620001</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>sound_break_1.wav</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>破碎1</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D155" s="0" t="n">
@@ -3883,16 +3883,16 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1000003</v>
+        <v>1000002</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>music_fight_3.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐3</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D156" s="0" t="n">
@@ -3901,16 +3901,16 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1000004</v>
+        <v>1000003</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>music_fight_4.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐4</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D157" s="0" t="n">
@@ -3919,16 +3919,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1000005</v>
+        <v>1000004</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D158" s="0" t="n">
@@ -3937,16 +3937,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1000006</v>
+        <v>1000005</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D159" s="0" t="n">
@@ -3955,16 +3955,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1000007</v>
+        <v>1000006</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D160" s="0" t="n">
@@ -3973,16 +3973,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1000008</v>
+        <v>1000007</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D161" s="0" t="n">
@@ -3991,16 +3991,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1000009</v>
+        <v>1000008</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D162" s="0" t="n">
@@ -4009,16 +4009,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1000010</v>
+        <v>1000009</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -4027,16 +4027,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1000011</v>
+        <v>1000010</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -4045,16 +4045,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1100001</v>
+        <v>1000011</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -4063,16 +4063,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1100002</v>
+        <v>1100001</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -4081,16 +4081,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1100003</v>
+        <v>1100002</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -4099,16 +4099,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1100004</v>
+        <v>1100003</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -4117,16 +4117,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1100005</v>
+        <v>1100004</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
@@ -4135,16 +4135,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1100006</v>
+        <v>1100005</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -4153,16 +4153,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -4171,16 +4171,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1100008</v>
+        <v>1100007</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -4189,16 +4189,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1100009</v>
+        <v>1100008</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D173" s="0" t="n">
@@ -4207,16 +4207,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1100010</v>
+        <v>1100009</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -4225,16 +4225,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1100011</v>
+        <v>1100010</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_10.wav</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐10</t>
         </is>
       </c>
       <c r="D175" s="0" t="n">
@@ -4243,16 +4243,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1100012</v>
+        <v>1100011</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_11.mp3</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐11</t>
         </is>
       </c>
       <c r="D176" s="0" t="n">
@@ -4261,16 +4261,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>1100013</v>
+        <v>1100012</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_12.mp3</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐12</t>
         </is>
       </c>
       <c r="D177" s="0" t="n">
@@ -4279,19 +4279,37 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B178" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B178" s="0" t="inlineStr">
+      <c r="B179" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C178" s="0" t="inlineStr">
+      <c r="C179" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D178" s="0" t="n">
+      <c r="D179" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -3595,16 +3595,16 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="n">
-        <v>530001</v>
+        <v>520002</v>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>sound_thunder_1.wav</t>
+          <t>sound_show_2.wav</t>
         </is>
       </c>
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>雷电1</t>
+          <t>展示2</t>
         </is>
       </c>
       <c r="D140" s="0" t="n">
@@ -3612,35 +3612,35 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="0" t="n">
-        <v>540001</v>
-      </c>
-      <c r="B141" s="0" t="inlineStr">
-        <is>
-          <t>sound_thunderstorm_1.wav</t>
-        </is>
-      </c>
-      <c r="C141" s="0" t="inlineStr">
-        <is>
-          <t>雷暴1</t>
-        </is>
-      </c>
-      <c r="D141" s="0" t="n">
+      <c r="A141" t="n">
+        <v>520003</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>sound_show_3.wav</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>展示3</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="n">
-        <v>550001</v>
+        <v>530001</v>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>sound_time_countdown_1.wav</t>
+          <t>sound_thunder_1.wav</t>
         </is>
       </c>
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>时间倒计时1</t>
+          <t>雷电1</t>
         </is>
       </c>
       <c r="D142" s="0" t="n">
@@ -3649,16 +3649,16 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="n">
-        <v>560001</v>
+        <v>540001</v>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>sound_turntable_1.wav</t>
+          <t>sound_thunderstorm_1.wav</t>
         </is>
       </c>
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>转盘1</t>
+          <t>雷暴1</t>
         </is>
       </c>
       <c r="D143" s="0" t="n">
@@ -3667,16 +3667,16 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="n">
-        <v>570001</v>
+        <v>550001</v>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>sound_walk_1.wav</t>
+          <t>sound_time_countdown_1.wav</t>
         </is>
       </c>
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>行走1</t>
+          <t>时间倒计时1</t>
         </is>
       </c>
       <c r="D144" s="0" t="n">
@@ -3685,16 +3685,16 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="n">
-        <v>580001</v>
+        <v>560001</v>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>sound_win_1.wav</t>
+          <t>sound_turntable_1.wav</t>
         </is>
       </c>
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>胜利1</t>
+          <t>转盘1</t>
         </is>
       </c>
       <c r="D145" s="0" t="n">
@@ -3703,16 +3703,16 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="n">
-        <v>580003</v>
+        <v>570001</v>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>sound_win_3.wav</t>
+          <t>sound_walk_1.wav</t>
         </is>
       </c>
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>胜利3</t>
+          <t>行走1</t>
         </is>
       </c>
       <c r="D146" s="0" t="n">
@@ -3721,16 +3721,16 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="n">
-        <v>580004</v>
+        <v>580001</v>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>sound_win_4.wav</t>
+          <t>sound_win_1.wav</t>
         </is>
       </c>
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>胜利4</t>
+          <t>胜利1</t>
         </is>
       </c>
       <c r="D147" s="0" t="n">
@@ -3739,16 +3739,16 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="n">
-        <v>590001</v>
+        <v>580003</v>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>sound_continuous_1.wav</t>
+          <t>sound_win_3.wav</t>
         </is>
       </c>
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>持续1</t>
+          <t>胜利3</t>
         </is>
       </c>
       <c r="D148" s="0" t="n">
@@ -3757,16 +3757,16 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="n">
-        <v>600001</v>
+        <v>580004</v>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_1.wav</t>
+          <t>sound_win_4.wav</t>
         </is>
       </c>
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>魔法1</t>
+          <t>胜利4</t>
         </is>
       </c>
       <c r="D149" s="0" t="n">
@@ -3775,16 +3775,16 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="n">
-        <v>600002</v>
+        <v>590001</v>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_2.wav</t>
+          <t>sound_continuous_1.wav</t>
         </is>
       </c>
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>魔法2</t>
+          <t>持续1</t>
         </is>
       </c>
       <c r="D150" s="0" t="n">
@@ -3793,16 +3793,16 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="n">
-        <v>600003</v>
+        <v>600001</v>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>sound_magic_3.wav</t>
+          <t>sound_magic_1.wav</t>
         </is>
       </c>
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>魔法3</t>
+          <t>魔法1</t>
         </is>
       </c>
       <c r="D151" s="0" t="n">
@@ -3811,16 +3811,16 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="n">
-        <v>610001</v>
+        <v>600002</v>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>sound_building_1.wav</t>
+          <t>sound_magic_2.wav</t>
         </is>
       </c>
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>建造1</t>
+          <t>魔法2</t>
         </is>
       </c>
       <c r="D152" s="0" t="n">
@@ -3829,16 +3829,16 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="n">
-        <v>610002</v>
+        <v>600003</v>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>sound_building_2.wav</t>
+          <t>sound_magic_3.wav</t>
         </is>
       </c>
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>建造2</t>
+          <t>魔法3</t>
         </is>
       </c>
       <c r="D153" s="0" t="n">
@@ -3846,71 +3846,71 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
-        <v>620001</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>sound_break_1.wav</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>破碎1</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
+      <c r="A154" s="0" t="n">
+        <v>610001</v>
+      </c>
+      <c r="B154" s="0" t="inlineStr">
+        <is>
+          <t>sound_building_1.wav</t>
+        </is>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>建造1</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="n">
-        <v>1000001</v>
+        <v>610002</v>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>music_fight_1.wav</t>
+          <t>sound_building_2.wav</t>
         </is>
       </c>
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐1</t>
+          <t>建造2</t>
         </is>
       </c>
       <c r="D155" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="n">
-        <v>1000002</v>
+        <v>620001</v>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>sound_break_1.wav</t>
         </is>
       </c>
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>破碎1</t>
         </is>
       </c>
       <c r="D156" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="n">
-        <v>1000003</v>
+        <v>1000001</v>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>music_fight_3.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐3</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D157" s="0" t="n">
@@ -3919,16 +3919,16 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="n">
-        <v>1000004</v>
+        <v>1000002</v>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>music_fight_4.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐4</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D158" s="0" t="n">
@@ -3937,16 +3937,16 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="n">
-        <v>1000005</v>
+        <v>1000003</v>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D159" s="0" t="n">
@@ -3955,16 +3955,16 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="n">
-        <v>1000006</v>
+        <v>1000004</v>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D160" s="0" t="n">
@@ -3973,16 +3973,16 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1000007</v>
+        <v>1000005</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D161" s="0" t="n">
@@ -3991,16 +3991,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1000008</v>
+        <v>1000006</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D162" s="0" t="n">
@@ -4009,16 +4009,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1000009</v>
+        <v>1000007</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -4027,16 +4027,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1000010</v>
+        <v>1000008</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -4045,16 +4045,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1000011</v>
+        <v>1000009</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -4063,16 +4063,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1100001</v>
+        <v>1000010</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -4081,16 +4081,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1100002</v>
+        <v>1000011</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -4099,16 +4099,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1100003</v>
+        <v>1100001</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -4117,16 +4117,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1100004</v>
+        <v>1100002</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
@@ -4135,16 +4135,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1100005</v>
+        <v>1100003</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -4153,16 +4153,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1100006</v>
+        <v>1100004</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -4171,16 +4171,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1100007</v>
+        <v>1100005</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -4189,16 +4189,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1100008</v>
+        <v>1100006</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D173" s="0" t="n">
@@ -4207,16 +4207,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1100009</v>
+        <v>1100007</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -4225,16 +4225,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1100010</v>
+        <v>1100008</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D175" s="0" t="n">
@@ -4243,16 +4243,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1100011</v>
+        <v>1100009</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D176" s="0" t="n">
@@ -4261,16 +4261,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>1100012</v>
+        <v>1100010</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_10.wav</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐10</t>
         </is>
       </c>
       <c r="D177" s="0" t="n">
@@ -4279,16 +4279,16 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>1100013</v>
+        <v>1100011</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_11.mp3</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐11</t>
         </is>
       </c>
       <c r="D178" s="0" t="n">
@@ -4297,19 +4297,55 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="B179" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_12.mp3</t>
+        </is>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐12</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B180" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B179" s="0" t="inlineStr">
+      <c r="B181" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C179" s="0" t="inlineStr">
+      <c r="C181" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D179" s="0" t="n">
+      <c r="D181" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -3612,20 +3612,20 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="0" t="n">
         <v>520003</v>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="0" t="inlineStr">
         <is>
           <t>sound_show_3.wav</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="0" t="inlineStr">
         <is>
           <t>展示3</t>
         </is>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3900,89 +3900,89 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="B157" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_1.wav</t>
-        </is>
-      </c>
-      <c r="C157" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐1</t>
-        </is>
-      </c>
-      <c r="D157" s="0" t="n">
-        <v>1</v>
+      <c r="A157" t="n">
+        <v>630001</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>sound_water_1.wav</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>水1</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="0" t="n">
-        <v>1000002</v>
-      </c>
-      <c r="B158" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_2.wav</t>
-        </is>
-      </c>
-      <c r="C158" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐2</t>
-        </is>
-      </c>
-      <c r="D158" s="0" t="n">
-        <v>1</v>
+      <c r="A158" t="n">
+        <v>630002</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>sound_water_2.wav</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>水2</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="0" t="n">
-        <v>1000003</v>
-      </c>
-      <c r="B159" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_3.wav</t>
-        </is>
-      </c>
-      <c r="C159" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐3</t>
-        </is>
-      </c>
-      <c r="D159" s="0" t="n">
-        <v>1</v>
+      <c r="A159" t="n">
+        <v>630003</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>sound_water_3.wav</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>水3</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="0" t="n">
-        <v>1000004</v>
-      </c>
-      <c r="B160" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_4.wav</t>
-        </is>
-      </c>
-      <c r="C160" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐4</t>
-        </is>
-      </c>
-      <c r="D160" s="0" t="n">
-        <v>1</v>
+      <c r="A160" t="n">
+        <v>630004</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>sound_water_4.wav</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>水4</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="n">
-        <v>1000005</v>
+        <v>1000001</v>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D161" s="0" t="n">
@@ -3991,16 +3991,16 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1000006</v>
+        <v>1000002</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D162" s="0" t="n">
@@ -4009,16 +4009,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1000007</v>
+        <v>1000003</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -4027,16 +4027,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1000008</v>
+        <v>1000004</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -4045,16 +4045,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1000009</v>
+        <v>1000005</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -4063,16 +4063,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1000010</v>
+        <v>1000006</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -4081,16 +4081,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1000011</v>
+        <v>1000007</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -4099,16 +4099,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1100001</v>
+        <v>1000008</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -4117,16 +4117,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1100002</v>
+        <v>1000009</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
@@ -4135,16 +4135,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1100003</v>
+        <v>1000010</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -4153,16 +4153,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1100004</v>
+        <v>1000011</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -4171,16 +4171,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1100005</v>
+        <v>1100001</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -4189,16 +4189,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1100006</v>
+        <v>1100002</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D173" s="0" t="n">
@@ -4207,16 +4207,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1100007</v>
+        <v>1100003</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -4225,16 +4225,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1100008</v>
+        <v>1100004</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D175" s="0" t="n">
@@ -4243,16 +4243,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1100009</v>
+        <v>1100005</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D176" s="0" t="n">
@@ -4261,16 +4261,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>1100010</v>
+        <v>1100006</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D177" s="0" t="n">
@@ -4279,16 +4279,16 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>1100011</v>
+        <v>1100007</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D178" s="0" t="n">
@@ -4297,16 +4297,16 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>1100012</v>
+        <v>1100008</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D179" s="0" t="n">
@@ -4315,16 +4315,16 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>1100013</v>
+        <v>1100009</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D180" s="0" t="n">
@@ -4333,19 +4333,91 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
+        <v>1100010</v>
+      </c>
+      <c r="B181" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_10.wav</t>
+        </is>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐10</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0" t="n">
+        <v>1100011</v>
+      </c>
+      <c r="B182" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_11.mp3</t>
+        </is>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐11</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0" t="n">
+        <v>1100012</v>
+      </c>
+      <c r="B183" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_12.mp3</t>
+        </is>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐12</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B184" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D184" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B181" s="0" t="inlineStr">
+      <c r="B185" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C181" s="0" t="inlineStr">
+      <c r="C185" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D181" s="0" t="n">
+      <c r="D185" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -3900,107 +3900,107 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" s="0" t="n">
         <v>630001</v>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="0" t="inlineStr">
         <is>
           <t>sound_water_1.wav</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" s="0" t="inlineStr">
         <is>
           <t>水1</t>
         </is>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" s="0" t="n">
         <v>630002</v>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="0" t="inlineStr">
         <is>
           <t>sound_water_2.wav</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="0" t="inlineStr">
         <is>
           <t>水2</t>
         </is>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" s="0" t="n">
         <v>630003</v>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="0" t="inlineStr">
         <is>
           <t>sound_water_3.wav</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="0" t="inlineStr">
         <is>
           <t>水3</t>
         </is>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" s="0" t="n">
         <v>630004</v>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="0" t="inlineStr">
         <is>
           <t>sound_water_4.wav</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C160" s="0" t="inlineStr">
         <is>
           <t>水4</t>
         </is>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="B161" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_1.wav</t>
-        </is>
-      </c>
-      <c r="C161" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐1</t>
-        </is>
-      </c>
-      <c r="D161" s="0" t="n">
-        <v>1</v>
+      <c r="A161" t="n">
+        <v>630005</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>sound_slime_1.wav</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>史莱姆1</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D162" s="0" t="n">
@@ -4009,16 +4009,16 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1000003</v>
+        <v>1000002</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>music_fight_3.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐3</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -4027,16 +4027,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1000004</v>
+        <v>1000003</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>music_fight_4.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐4</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -4045,16 +4045,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1000005</v>
+        <v>1000004</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -4063,16 +4063,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1000006</v>
+        <v>1000005</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -4081,16 +4081,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1000007</v>
+        <v>1000006</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -4099,16 +4099,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1000008</v>
+        <v>1000007</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -4117,16 +4117,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1000009</v>
+        <v>1000008</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
@@ -4135,16 +4135,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1000010</v>
+        <v>1000009</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -4153,16 +4153,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1000011</v>
+        <v>1000010</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -4171,16 +4171,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1100001</v>
+        <v>1000011</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -4189,16 +4189,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1100002</v>
+        <v>1100001</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D173" s="0" t="n">
@@ -4207,16 +4207,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1100003</v>
+        <v>1100002</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -4225,16 +4225,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1100004</v>
+        <v>1100003</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D175" s="0" t="n">
@@ -4243,16 +4243,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1100005</v>
+        <v>1100004</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D176" s="0" t="n">
@@ -4261,16 +4261,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>1100006</v>
+        <v>1100005</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D177" s="0" t="n">
@@ -4279,16 +4279,16 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D178" s="0" t="n">
@@ -4297,16 +4297,16 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>1100008</v>
+        <v>1100007</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D179" s="0" t="n">
@@ -4315,16 +4315,16 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>1100009</v>
+        <v>1100008</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D180" s="0" t="n">
@@ -4333,16 +4333,16 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>1100010</v>
+        <v>1100009</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D181" s="0" t="n">
@@ -4351,16 +4351,16 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>1100011</v>
+        <v>1100010</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_10.wav</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐10</t>
         </is>
       </c>
       <c r="D182" s="0" t="n">
@@ -4369,16 +4369,16 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>1100012</v>
+        <v>1100011</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_11.mp3</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐11</t>
         </is>
       </c>
       <c r="D183" s="0" t="n">
@@ -4387,16 +4387,16 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>1100013</v>
+        <v>1100012</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_12.mp3</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐12</t>
         </is>
       </c>
       <c r="D184" s="0" t="n">
@@ -4405,19 +4405,37 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
+        <v>1100013</v>
+      </c>
+      <c r="B185" s="0" t="inlineStr">
+        <is>
+          <t>music_gaming_13.mp3</t>
+        </is>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>游戏中音乐13</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0" t="n">
         <v>1200001</v>
       </c>
-      <c r="B185" s="0" t="inlineStr">
+      <c r="B186" s="0" t="inlineStr">
         <is>
           <t>music_main_1.wav</t>
         </is>
       </c>
-      <c r="C185" s="0" t="inlineStr">
+      <c r="C186" s="0" t="inlineStr">
         <is>
           <t>主界面音乐1</t>
         </is>
       </c>
-      <c r="D185" s="0" t="n">
+      <c r="D186" s="0" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -3972,20 +3972,20 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" s="0" t="n">
         <v>630005</v>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="0" t="inlineStr">
         <is>
           <t>sound_slime_1.wav</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C161" s="0" t="inlineStr">
         <is>
           <t>史莱姆1</t>
         </is>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4437,6 +4437,24 @@
       </c>
       <c r="D186" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>sound_night_1.wav</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>夜晚虫鸣1</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E188"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -4440,20 +4440,38 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
+      <c r="A187" s="0" t="n">
         <v>2000001</v>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B187" s="0" t="inlineStr">
         <is>
           <t>sound_night_1.wav</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C187" s="0" t="inlineStr">
         <is>
           <t>夜晚虫鸣1</t>
         </is>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>2000002</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>sound_rain_1.wav</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>下雨1</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
         <v>2</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_audio_info[音频信息_FrameWork].xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E188"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="47.5" customWidth="1" style="1" min="2" max="2"/>
@@ -3990,35 +3990,35 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="0" t="n">
-        <v>1000001</v>
-      </c>
-      <c r="B162" s="0" t="inlineStr">
-        <is>
-          <t>music_fight_1.wav</t>
-        </is>
-      </c>
-      <c r="C162" s="0" t="inlineStr">
-        <is>
-          <t>战斗音乐1</t>
-        </is>
-      </c>
-      <c r="D162" s="0" t="n">
-        <v>1</v>
+      <c r="A162" t="n">
+        <v>640001</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>sound_talk_1.wav</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>对话说话1</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="n">
-        <v>1000002</v>
+        <v>1000001</v>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>music_fight_2.wav</t>
+          <t>music_fight_1.wav</t>
         </is>
       </c>
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐2</t>
+          <t>战斗音乐1</t>
         </is>
       </c>
       <c r="D163" s="0" t="n">
@@ -4027,16 +4027,16 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="n">
-        <v>1000003</v>
+        <v>1000002</v>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>music_fight_3.wav</t>
+          <t>music_fight_2.wav</t>
         </is>
       </c>
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐3</t>
+          <t>战斗音乐2</t>
         </is>
       </c>
       <c r="D164" s="0" t="n">
@@ -4045,16 +4045,16 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="n">
-        <v>1000004</v>
+        <v>1000003</v>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>music_fight_4.wav</t>
+          <t>music_fight_3.wav</t>
         </is>
       </c>
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐4</t>
+          <t>战斗音乐3</t>
         </is>
       </c>
       <c r="D165" s="0" t="n">
@@ -4063,16 +4063,16 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="n">
-        <v>1000005</v>
+        <v>1000004</v>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>music_fight_5.wav</t>
+          <t>music_fight_4.wav</t>
         </is>
       </c>
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐5</t>
+          <t>战斗音乐4</t>
         </is>
       </c>
       <c r="D166" s="0" t="n">
@@ -4081,16 +4081,16 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="n">
-        <v>1000006</v>
+        <v>1000005</v>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>music_fight_6.wav</t>
+          <t>music_fight_5.wav</t>
         </is>
       </c>
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐6</t>
+          <t>战斗音乐5</t>
         </is>
       </c>
       <c r="D167" s="0" t="n">
@@ -4099,16 +4099,16 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="n">
-        <v>1000007</v>
+        <v>1000006</v>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>music_fight_7.wav</t>
+          <t>music_fight_6.wav</t>
         </is>
       </c>
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐7</t>
+          <t>战斗音乐6</t>
         </is>
       </c>
       <c r="D168" s="0" t="n">
@@ -4117,16 +4117,16 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="n">
-        <v>1000008</v>
+        <v>1000007</v>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>music_fight_8.wav</t>
+          <t>music_fight_7.wav</t>
         </is>
       </c>
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐8</t>
+          <t>战斗音乐7</t>
         </is>
       </c>
       <c r="D169" s="0" t="n">
@@ -4135,16 +4135,16 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="n">
-        <v>1000009</v>
+        <v>1000008</v>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>music_fight_9.mp3</t>
+          <t>music_fight_8.wav</t>
         </is>
       </c>
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐9</t>
+          <t>战斗音乐8</t>
         </is>
       </c>
       <c r="D170" s="0" t="n">
@@ -4153,16 +4153,16 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="n">
-        <v>1000010</v>
+        <v>1000009</v>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>music_fight_10.mp3</t>
+          <t>music_fight_9.mp3</t>
         </is>
       </c>
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐10</t>
+          <t>战斗音乐9</t>
         </is>
       </c>
       <c r="D171" s="0" t="n">
@@ -4171,16 +4171,16 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="n">
-        <v>1000011</v>
+        <v>1000010</v>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>music_fight_11.mp3</t>
+          <t>music_fight_10.mp3</t>
         </is>
       </c>
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>战斗音乐11</t>
+          <t>战斗音乐10</t>
         </is>
       </c>
       <c r="D172" s="0" t="n">
@@ -4189,16 +4189,16 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="n">
-        <v>1100001</v>
+        <v>1000011</v>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_1.wav</t>
+          <t>music_fight_11.mp3</t>
         </is>
       </c>
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐1</t>
+          <t>战斗音乐11</t>
         </is>
       </c>
       <c r="D173" s="0" t="n">
@@ -4207,16 +4207,16 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="n">
-        <v>1100002</v>
+        <v>1100001</v>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_2.wav</t>
+          <t>music_gaming_1.wav</t>
         </is>
       </c>
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐2</t>
+          <t>游戏中音乐1</t>
         </is>
       </c>
       <c r="D174" s="0" t="n">
@@ -4225,16 +4225,16 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="n">
-        <v>1100003</v>
+        <v>1100002</v>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_3.wav</t>
+          <t>music_gaming_2.wav</t>
         </is>
       </c>
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐3</t>
+          <t>游戏中音乐2</t>
         </is>
       </c>
       <c r="D175" s="0" t="n">
@@ -4243,16 +4243,16 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="n">
-        <v>1100004</v>
+        <v>1100003</v>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_4.wav</t>
+          <t>music_gaming_3.wav</t>
         </is>
       </c>
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐4</t>
+          <t>游戏中音乐3</t>
         </is>
       </c>
       <c r="D176" s="0" t="n">
@@ -4261,16 +4261,16 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="n">
-        <v>1100005</v>
+        <v>1100004</v>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_5.wav</t>
+          <t>music_gaming_4.wav</t>
         </is>
       </c>
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐5</t>
+          <t>游戏中音乐4</t>
         </is>
       </c>
       <c r="D177" s="0" t="n">
@@ -4279,16 +4279,16 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="n">
-        <v>1100006</v>
+        <v>1100005</v>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_6.wav</t>
+          <t>music_gaming_5.wav</t>
         </is>
       </c>
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐6</t>
+          <t>游戏中音乐5</t>
         </is>
       </c>
       <c r="D178" s="0" t="n">
@@ -4297,16 +4297,16 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="n">
-        <v>1100007</v>
+        <v>1100006</v>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_7.wav</t>
+          <t>music_gaming_6.wav</t>
         </is>
       </c>
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐7</t>
+          <t>游戏中音乐6</t>
         </is>
       </c>
       <c r="D179" s="0" t="n">
@@ -4315,16 +4315,16 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="n">
-        <v>1100008</v>
+        <v>1100007</v>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_8.wav</t>
+          <t>music_gaming_7.wav</t>
         </is>
       </c>
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐8</t>
+          <t>游戏中音乐7</t>
         </is>
       </c>
       <c r="D180" s="0" t="n">
@@ -4333,16 +4333,16 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="n">
-        <v>1100009</v>
+        <v>1100008</v>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_9.wav</t>
+          <t>music_gaming_8.wav</t>
         </is>
       </c>
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐9</t>
+          <t>游戏中音乐8</t>
         </is>
       </c>
       <c r="D181" s="0" t="n">
@@ -4351,16 +4351,16 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="n">
-        <v>1100010</v>
+        <v>1100009</v>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_10.wav</t>
+          <t>music_gaming_9.wav</t>
         </is>
       </c>
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐10</t>
+          <t>游戏中音乐9</t>
         </is>
       </c>
       <c r="D182" s="0" t="n">
@@ -4369,16 +4369,16 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="n">
-        <v>1100011</v>
+        <v>1100010</v>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_11.mp3</t>
+          <t>music_gaming_10.wav</t>
         </is>
       </c>
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐11</t>
+          <t>游戏中音乐10</t>
         </is>
       </c>
       <c r="D183" s="0" t="n">
@@ -4387,16 +4387,16 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="n">
-        <v>1100012</v>
+        <v>1100011</v>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_12.mp3</t>
+          <t>music_gaming_11.mp3</t>
         </is>
       </c>
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐12</t>
+          <t>游戏中音乐11</t>
         </is>
       </c>
       <c r="D184" s="0" t="n">
@@ -4405,16 +4405,16 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="n">
-        <v>1100013</v>
+        <v>1100012</v>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>music_gaming_13.mp3</t>
+          <t>music_gaming_12.mp3</t>
         </is>
       </c>
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>游戏中音乐13</t>
+          <t>游戏中音乐12</t>
         </is>
       </c>
       <c r="D185" s="0" t="n">
@@ -4423,16 +4423,16 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="n">
-        <v>1200001</v>
+        <v>1100013</v>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>music_main_1.wav</t>
+          <t>music_gaming_13.mp3</t>
         </is>
       </c>
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>主界面音乐1</t>
+          <t>游戏中音乐13</t>
         </is>
       </c>
       <c r="D186" s="0" t="n">
@@ -4441,37 +4441,55 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="n">
+        <v>1200001</v>
+      </c>
+      <c r="B187" s="0" t="inlineStr">
+        <is>
+          <t>music_main_1.wav</t>
+        </is>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>主界面音乐1</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0" t="n">
         <v>2000001</v>
       </c>
-      <c r="B187" s="0" t="inlineStr">
+      <c r="B188" s="0" t="inlineStr">
         <is>
           <t>sound_night_1.wav</t>
         </is>
       </c>
-      <c r="C187" s="0" t="inlineStr">
+      <c r="C188" s="0" t="inlineStr">
         <is>
           <t>夜晚虫鸣1</t>
         </is>
       </c>
-      <c r="D187" s="0" t="n">
+      <c r="D188" s="0" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="n">
+    <row r="189">
+      <c r="A189" s="0" t="n">
         <v>2000002</v>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B189" s="0" t="inlineStr">
         <is>
           <t>sound_rain_1.wav</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C189" s="0" t="inlineStr">
         <is>
           <t>下雨1</t>
         </is>
       </c>
-      <c r="D188" t="n">
+      <c r="D189" s="0" t="n">
         <v>2</v>
       </c>
     </row>
